--- a/resultados/motores_calculados.xlsx
+++ b/resultados/motores_calculados.xlsx
@@ -7,9 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MOTORES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RESUMEN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +32,35 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +74,52 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,236 +488,374 @@
   </sheetPr>
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>TAG</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>VOLTAJE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>EFICIENCIA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CORRIENTE_PLACA_A</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>CORRIENTE_MEDIDA_A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>KW</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>CORRIENTE_CALCULADA_A</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>DESVIACION_CALC_PLACA_PCT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>CARGA_CORRIENTE_PCT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>ALERTA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>M-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Bomba de agua</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.88</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>93.25</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="5" t="n">
         <v>135.59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="5" t="n">
         <v>-3.15</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="5" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>M-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Ventilador</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="5" t="n">
         <v>0.93</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>55.95</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="5" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="5" t="n">
         <v>-1.95</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="5" t="n">
         <v>92.68000000000001</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>M-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Bomba condensado</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>22.38</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="5" t="n">
         <v>-2.85</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="5" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Total de motores</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Potencia instalada HP</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Potencia instalada kW</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>171.58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Motores normales</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Motores con carga alta</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Motores con carga baja</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Motores con posible sobrecarga</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Corriente calculada total A</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>249.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Corriente medida total A</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resultados/motores_calculados.xlsx
+++ b/resultados/motores_calculados.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -854,8 +854,38 @@
         <v>228</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Límite carga baja %</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Límite carga alta %</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Límite sobrecarga %</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resultados/motores_calculados.xlsx
+++ b/resultados/motores_calculados.xlsx
@@ -11,8 +11,8 @@
     <sheet name="RESUMEN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$AB$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,25 +106,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,23 +488,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
+    <col width="42" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -543,37 +559,107 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CORRIENTE_MEDIDA_A</t>
+          <t>CORRIENTE_L1_A</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>CORRIENTE_L2_A</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>CORRIENTE_L3_A</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAJE_L1_L2_V</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAJE_L2_L3_V</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAJE_L3_L1_V</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>KW</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>CORRIENTE_CALCULADA_A</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>DESVIACION_CALC_PLACA_PCT</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>CORRIENTE_PROMEDIO_A</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>DESBALANCE_CORRIENTE_PCT</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>FASE_MAYOR_CORRIENTE</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>FASE_MENOR_CORRIENTE</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAJE_PROMEDIO_V</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>DESBALANCE_VOLTAJE_PCT</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>CARGA_CORRIENTE_PCT</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>ALERTA</t>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>ALERTA_CARGA</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>ALERTA_DESBALANCE_CORRIENTE</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>ALERTA_DESBALANCE_VOLTAJE</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>DIAGNOSTICO_GENERAL</t>
         </is>
       </c>
     </row>
@@ -583,47 +669,99 @@
           <t>M-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Bomba de agua</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>478</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>481</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="O2" s="4" t="n">
         <v>93.25</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="P2" s="4" t="n">
         <v>135.59</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="Q2" s="4" t="n">
         <v>-3.15</v>
       </c>
-      <c r="M2" s="5" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="R2" s="4" t="n">
+        <v>120.33</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -635,47 +773,99 @@
           <t>M-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Ventilador</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>477</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>482</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="O3" s="4" t="n">
         <v>55.95</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="P3" s="4" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="Q3" s="4" t="n">
         <v>-1.95</v>
       </c>
-      <c r="M3" s="5" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="R3" s="4" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>479.67</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>CARGA ALTA</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
@@ -687,54 +877,106 @@
           <t>M-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Bomba condensado</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>479</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>478</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>481</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="O4" s="4" t="n">
         <v>22.38</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="P4" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="Q4" s="4" t="n">
         <v>-2.85</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="R4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X4" s="4" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
       </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="AB4" s="7" t="inlineStr">
+        <is>
+          <t>CARGA ALTA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:AB4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -745,11 +987,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -765,127 +1007,177 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Total de motores</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Potencia instalada HP</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="4" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Potencia instalada kW</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="4" t="n">
         <v>171.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Motores normales</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Motores diagnóstico normal</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Motores con carga alta</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Motores con carga baja</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Motores con posible sobrecarga</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Corriente calculada total A</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>249.99</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Motores con desbalance de corriente</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Corriente medida total A</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>228</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Motores con desbalance de voltaje</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Mayor desbalance de corriente %</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Mayor desbalance de voltaje %</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Carga promedio por corriente %</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>90.16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Límite carga baja %</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B14" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Límite carga alta %</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B15" s="4" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Límite sobrecarga %</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B16" s="4" t="n">
         <v>100</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Límite desbalance corriente %</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Límite desbalance voltaje %</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resultados/motores_calculados.xlsx
+++ b/resultados/motores_calculados.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,12 +112,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -865,7 +859,7 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AB3" s="7" t="inlineStr">
+      <c r="AB3" s="6" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
@@ -969,7 +963,7 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AB4" s="7" t="inlineStr">
+      <c r="AB4" s="6" t="inlineStr">
         <is>
           <t>CARGA ALTA</t>
         </is>
@@ -994,185 +988,185 @@
     <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>INDICADOR</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Total de motores</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Potencia instalada HP</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="9" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Potencia instalada kW</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="9" t="n">
         <v>171.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Motores diagnóstico normal</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Motores con carga alta</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Motores con carga baja</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Motores con posible sobrecarga</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Motores con desbalance de corriente</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Motores con desbalance de voltaje</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Mayor desbalance de corriente %</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="9" t="n">
         <v>3.49</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Mayor desbalance de voltaje %</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Carga promedio por corriente %</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="9" t="n">
         <v>90.16</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Límite carga baja %</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="9" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Límite carga alta %</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="9" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Límite sobrecarga %</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="9" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Límite desbalance corriente %</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="9" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Límite desbalance voltaje %</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/resultados/motores_calculados.xlsx
+++ b/resultados/motores_calculados.xlsx
@@ -11,7 +11,7 @@
     <sheet name="RESUMEN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$AB$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOTORES'!$A$1:$BG$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RESUMEN'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -56,7 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,11 +94,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -104,6 +107,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -482,495 +488,4069 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="42" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="18" customWidth="1" min="43" max="43"/>
+    <col width="25" customWidth="1" min="44" max="44"/>
+    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="28" customWidth="1" min="48" max="48"/>
+    <col width="23" customWidth="1" min="49" max="49"/>
+    <col width="27" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="51" max="51"/>
+    <col width="23" customWidth="1" min="52" max="52"/>
+    <col width="21" customWidth="1" min="53" max="53"/>
+    <col width="25" customWidth="1" min="54" max="54"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="15" customWidth="1" min="56" max="56"/>
+    <col width="30" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="42" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TAG</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>AREA</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>FABRICANTE</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>TIPO_EQUIPO</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>KW_PLACA</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>VOLTAJE</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>VOLTAJE_V</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CORRIENTE_PLACA_A</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>FRECUENCIA_HZ</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>FP</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>EFICIENCIA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>CORRIENTE_PLACA_A</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>CLASE_EFICIENCIA</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>RPM_MOTOR</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>RPM_SALIDA</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>RELACION_REDUCCION</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PAR_SALIDA_NM</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>SERVICIO</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR_SERVICIO</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>CLASE_AISLAMIENTO</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>INVERTER_DUTY</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURA_MIN_C</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURA_MAX_C</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>LUBRICANTE</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>VOLUMEN_ACEITE_L</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PESO_KG</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>FRENO</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>VOLTAJE_FRENO_V</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PAR_FRENO_NM</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>ESTADO_ACTIVO</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES_ACTIVO</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>CORRIENTE_L1_A</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>CORRIENTE_L2_A</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>CORRIENTE_L3_A</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="AL1" s="3" t="inlineStr">
         <is>
           <t>VOLTAJE_L1_L2_V</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="AM1" s="3" t="inlineStr">
         <is>
           <t>VOLTAJE_L2_L3_V</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="AN1" s="3" t="inlineStr">
         <is>
           <t>VOLTAJE_L3_L1_V</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>ESTADO</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURA_C</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>AISLAMIENTO_MOHM</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>ESTADO_MEDICION</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES_MEDICION</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>TIENE_MEDICION</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>KW_CALCULADO_HP</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
         <is>
           <t>CORRIENTE_CALCULADA_A</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="AV1" s="3" t="inlineStr">
         <is>
           <t>DESVIACION_CALC_PLACA_PCT</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="AW1" s="3" t="inlineStr">
         <is>
           <t>CORRIENTE_PROMEDIO_A</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="AX1" s="3" t="inlineStr">
         <is>
           <t>DESBALANCE_CORRIENTE_PCT</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="AY1" s="3" t="inlineStr">
         <is>
           <t>FASE_MAYOR_CORRIENTE</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="AZ1" s="3" t="inlineStr">
         <is>
           <t>FASE_MENOR_CORRIENTE</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="BA1" s="3" t="inlineStr">
         <is>
           <t>VOLTAJE_PROMEDIO_V</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="BB1" s="3" t="inlineStr">
         <is>
           <t>DESBALANCE_VOLTAJE_PCT</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="BC1" s="3" t="inlineStr">
         <is>
           <t>CARGA_CORRIENTE_PCT</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="BD1" s="3" t="inlineStr">
         <is>
           <t>ALERTA_CARGA</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="BE1" s="3" t="inlineStr">
         <is>
           <t>ALERTA_DESBALANCE_CORRIENTE</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="BF1" s="3" t="inlineStr">
         <is>
           <t>ALERTA_DESBALANCE_VOLTAJE</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="BG1" s="3" t="inlineStr">
         <is>
           <t>DIAGNOSTICO_GENERAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>M-001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Bomba de agua</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MR-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>123</v>
+      <c r="J2" s="5" t="n">
+        <v>6.9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>478</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>481</v>
-      </c>
-      <c r="M2" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE2" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF2" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH2" s="6" t="n">
+        <v>46322</v>
+      </c>
+      <c r="AI2" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ2" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AK2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" s="5" t="n">
+        <v>477</v>
+      </c>
+      <c r="AM2" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="AN2" s="5" t="n">
         <v>479</v>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="AO2" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AP2" s="4" t="n">
+        <v>810</v>
+      </c>
+      <c r="AQ2" s="4" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="O2" s="4" t="n">
-        <v>93.25</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>135.59</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>-3.15</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>120.33</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="AR2" s="4" t="inlineStr"/>
+      <c r="AS2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU2" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV2" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX2" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY2" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="AZ2" s="4" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="V2" s="4" t="n">
-        <v>479.33</v>
-      </c>
-      <c r="W2" s="4" t="n">
+      <c r="BA2" s="5" t="n">
+        <v>478.67</v>
+      </c>
+      <c r="BB2" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="X2" s="4" t="n">
-        <v>85.95</v>
-      </c>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="BC2" s="5" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="BD2" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="BE2" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="BF2" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AB2" s="5" t="inlineStr">
+      <c r="BG2" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>M-002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Ventilador</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MR-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>79</v>
+      <c r="J3" s="5" t="n">
+        <v>6.9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>477</v>
-      </c>
-      <c r="L3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>482</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="AE3" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="n">
+        <v>46292</v>
+      </c>
+      <c r="AI3" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK3" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AL3" s="5" t="n">
+        <v>479</v>
+      </c>
+      <c r="AM3" s="5" t="n">
+        <v>481</v>
+      </c>
+      <c r="AN3" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="AO3" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
         <is>
           <t>Operando</t>
         </is>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>76.33</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU3" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV3" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW3" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AX3" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY3" s="4" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>479.67</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>93.09</v>
-      </c>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>CARGA ALTA</t>
-        </is>
-      </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AZ3" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="BA3" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="BB3" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BC3" s="5" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="BD3" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="BE3" s="7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="AB3" s="6" t="inlineStr">
-        <is>
-          <t>CARGA ALTA</t>
+      <c r="BF3" s="7" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="BG3" s="7" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>M-003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Bomba condensado</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MR-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 3</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>33</v>
+      <c r="J4" s="5" t="n">
+        <v>6.9</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>479</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>478</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>481</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Operando</t>
+        <v>60</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
         </is>
       </c>
       <c r="O4" s="4" t="n">
-        <v>22.38</v>
+        <v>1758</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>-2.85</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>479.33</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0.35</v>
+        <v>1310</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="X4" s="4" t="n">
-        <v>91.43000000000001</v>
-      </c>
-      <c r="Y4" s="6" t="inlineStr">
-        <is>
-          <t>CARGA ALTA</t>
-        </is>
-      </c>
-      <c r="Z4" s="5" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="AA4" s="5" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="AB4" s="6" t="inlineStr">
-        <is>
-          <t>CARGA ALTA</t>
+        <v>-20</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="5" t="inlineStr"/>
+      <c r="AJ4" s="5" t="inlineStr"/>
+      <c r="AK4" s="5" t="inlineStr"/>
+      <c r="AL4" s="5" t="inlineStr"/>
+      <c r="AM4" s="5" t="inlineStr"/>
+      <c r="AN4" s="5" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU4" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV4" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW4" s="5" t="inlineStr"/>
+      <c r="AX4" s="5" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="5" t="inlineStr"/>
+      <c r="BB4" s="5" t="inlineStr"/>
+      <c r="BC4" s="5" t="inlineStr"/>
+      <c r="BD4" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE4" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF4" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG4" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MR-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 4</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="5" t="inlineStr"/>
+      <c r="AJ5" s="5" t="inlineStr"/>
+      <c r="AK5" s="5" t="inlineStr"/>
+      <c r="AL5" s="5" t="inlineStr"/>
+      <c r="AM5" s="5" t="inlineStr"/>
+      <c r="AN5" s="5" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU5" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW5" s="5" t="inlineStr"/>
+      <c r="AX5" s="5" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="5" t="inlineStr"/>
+      <c r="BB5" s="5" t="inlineStr"/>
+      <c r="BC5" s="5" t="inlineStr"/>
+      <c r="BD5" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE5" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF5" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG5" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MR-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE6" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF6" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="5" t="inlineStr"/>
+      <c r="AJ6" s="5" t="inlineStr"/>
+      <c r="AK6" s="5" t="inlineStr"/>
+      <c r="AL6" s="5" t="inlineStr"/>
+      <c r="AM6" s="5" t="inlineStr"/>
+      <c r="AN6" s="5" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU6" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV6" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW6" s="5" t="inlineStr"/>
+      <c r="AX6" s="5" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="5" t="inlineStr"/>
+      <c r="BB6" s="5" t="inlineStr"/>
+      <c r="BC6" s="5" t="inlineStr"/>
+      <c r="BD6" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE6" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF6" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG6" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MR-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 6</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE7" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="5" t="inlineStr"/>
+      <c r="AJ7" s="5" t="inlineStr"/>
+      <c r="AK7" s="5" t="inlineStr"/>
+      <c r="AL7" s="5" t="inlineStr"/>
+      <c r="AM7" s="5" t="inlineStr"/>
+      <c r="AN7" s="5" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU7" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV7" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW7" s="5" t="inlineStr"/>
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr"/>
+      <c r="BC7" s="5" t="inlineStr"/>
+      <c r="BD7" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE7" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF7" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG7" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MR-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 7</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="5" t="inlineStr"/>
+      <c r="AJ8" s="5" t="inlineStr"/>
+      <c r="AK8" s="5" t="inlineStr"/>
+      <c r="AL8" s="5" t="inlineStr"/>
+      <c r="AM8" s="5" t="inlineStr"/>
+      <c r="AN8" s="5" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU8" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW8" s="5" t="inlineStr"/>
+      <c r="AX8" s="5" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="5" t="inlineStr"/>
+      <c r="BB8" s="5" t="inlineStr"/>
+      <c r="BC8" s="5" t="inlineStr"/>
+      <c r="BD8" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE8" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF8" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG8" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>MR-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 8</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE9" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="5" t="inlineStr"/>
+      <c r="AJ9" s="5" t="inlineStr"/>
+      <c r="AK9" s="5" t="inlineStr"/>
+      <c r="AL9" s="5" t="inlineStr"/>
+      <c r="AM9" s="5" t="inlineStr"/>
+      <c r="AN9" s="5" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU9" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV9" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW9" s="5" t="inlineStr"/>
+      <c r="AX9" s="5" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="BB9" s="5" t="inlineStr"/>
+      <c r="BC9" s="5" t="inlineStr"/>
+      <c r="BD9" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE9" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF9" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG9" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MR-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 9</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD10" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE10" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="5" t="inlineStr"/>
+      <c r="AJ10" s="5" t="inlineStr"/>
+      <c r="AK10" s="5" t="inlineStr"/>
+      <c r="AL10" s="5" t="inlineStr"/>
+      <c r="AM10" s="5" t="inlineStr"/>
+      <c r="AN10" s="5" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="inlineStr"/>
+      <c r="AS10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU10" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV10" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW10" s="5" t="inlineStr"/>
+      <c r="AX10" s="5" t="inlineStr"/>
+      <c r="AY10" s="4" t="inlineStr"/>
+      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="BA10" s="5" t="inlineStr"/>
+      <c r="BB10" s="5" t="inlineStr"/>
+      <c r="BC10" s="5" t="inlineStr"/>
+      <c r="BD10" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE10" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF10" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG10" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MR-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 10</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE11" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="5" t="inlineStr"/>
+      <c r="AJ11" s="5" t="inlineStr"/>
+      <c r="AK11" s="5" t="inlineStr"/>
+      <c r="AL11" s="5" t="inlineStr"/>
+      <c r="AM11" s="5" t="inlineStr"/>
+      <c r="AN11" s="5" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU11" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV11" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW11" s="5" t="inlineStr"/>
+      <c r="AX11" s="5" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="5" t="inlineStr"/>
+      <c r="BB11" s="5" t="inlineStr"/>
+      <c r="BC11" s="5" t="inlineStr"/>
+      <c r="BD11" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE11" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF11" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG11" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MR-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 11</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE12" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="5" t="inlineStr"/>
+      <c r="AJ12" s="5" t="inlineStr"/>
+      <c r="AK12" s="5" t="inlineStr"/>
+      <c r="AL12" s="5" t="inlineStr"/>
+      <c r="AM12" s="5" t="inlineStr"/>
+      <c r="AN12" s="5" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU12" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV12" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW12" s="5" t="inlineStr"/>
+      <c r="AX12" s="5" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="5" t="inlineStr"/>
+      <c r="BB12" s="5" t="inlineStr"/>
+      <c r="BC12" s="5" t="inlineStr"/>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>MR-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 12</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE13" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG13" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AI13" s="5" t="inlineStr"/>
+      <c r="AJ13" s="5" t="inlineStr"/>
+      <c r="AK13" s="5" t="inlineStr"/>
+      <c r="AL13" s="5" t="inlineStr"/>
+      <c r="AM13" s="5" t="inlineStr"/>
+      <c r="AN13" s="5" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AP13" s="4" t="inlineStr"/>
+      <c r="AQ13" s="4" t="inlineStr"/>
+      <c r="AR13" s="4" t="inlineStr"/>
+      <c r="AS13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU13" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV13" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW13" s="5" t="inlineStr"/>
+      <c r="AX13" s="5" t="inlineStr"/>
+      <c r="AY13" s="4" t="inlineStr"/>
+      <c r="AZ13" s="4" t="inlineStr"/>
+      <c r="BA13" s="5" t="inlineStr"/>
+      <c r="BB13" s="5" t="inlineStr"/>
+      <c r="BC13" s="5" t="inlineStr"/>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MR-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 13</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB14" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE14" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="5" t="inlineStr"/>
+      <c r="AJ14" s="5" t="inlineStr"/>
+      <c r="AK14" s="5" t="inlineStr"/>
+      <c r="AL14" s="5" t="inlineStr"/>
+      <c r="AM14" s="5" t="inlineStr"/>
+      <c r="AN14" s="5" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr"/>
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU14" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV14" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW14" s="5" t="inlineStr"/>
+      <c r="AX14" s="5" t="inlineStr"/>
+      <c r="AY14" s="4" t="inlineStr"/>
+      <c r="AZ14" s="4" t="inlineStr"/>
+      <c r="BA14" s="5" t="inlineStr"/>
+      <c r="BB14" s="5" t="inlineStr"/>
+      <c r="BC14" s="5" t="inlineStr"/>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MR-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 14</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE15" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="5" t="inlineStr"/>
+      <c r="AJ15" s="5" t="inlineStr"/>
+      <c r="AK15" s="5" t="inlineStr"/>
+      <c r="AL15" s="5" t="inlineStr"/>
+      <c r="AM15" s="5" t="inlineStr"/>
+      <c r="AN15" s="5" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr"/>
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AS15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU15" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW15" s="5" t="inlineStr"/>
+      <c r="AX15" s="5" t="inlineStr"/>
+      <c r="AY15" s="4" t="inlineStr"/>
+      <c r="AZ15" s="4" t="inlineStr"/>
+      <c r="BA15" s="5" t="inlineStr"/>
+      <c r="BB15" s="5" t="inlineStr"/>
+      <c r="BC15" s="5" t="inlineStr"/>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MR-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 15</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE16" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AI16" s="5" t="inlineStr"/>
+      <c r="AJ16" s="5" t="inlineStr"/>
+      <c r="AK16" s="5" t="inlineStr"/>
+      <c r="AL16" s="5" t="inlineStr"/>
+      <c r="AM16" s="5" t="inlineStr"/>
+      <c r="AN16" s="5" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AP16" s="4" t="inlineStr"/>
+      <c r="AQ16" s="4" t="inlineStr"/>
+      <c r="AR16" s="4" t="inlineStr"/>
+      <c r="AS16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU16" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW16" s="5" t="inlineStr"/>
+      <c r="AX16" s="5" t="inlineStr"/>
+      <c r="AY16" s="4" t="inlineStr"/>
+      <c r="AZ16" s="4" t="inlineStr"/>
+      <c r="BA16" s="5" t="inlineStr"/>
+      <c r="BB16" s="5" t="inlineStr"/>
+      <c r="BC16" s="5" t="inlineStr"/>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MR-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 16</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE17" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG17" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="5" t="inlineStr"/>
+      <c r="AJ17" s="5" t="inlineStr"/>
+      <c r="AK17" s="5" t="inlineStr"/>
+      <c r="AL17" s="5" t="inlineStr"/>
+      <c r="AM17" s="5" t="inlineStr"/>
+      <c r="AN17" s="5" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr"/>
+      <c r="AS17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU17" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV17" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW17" s="5" t="inlineStr"/>
+      <c r="AX17" s="5" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="5" t="inlineStr"/>
+      <c r="BB17" s="5" t="inlineStr"/>
+      <c r="BC17" s="5" t="inlineStr"/>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MR-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 17</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD18" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE18" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF18" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG18" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr"/>
+      <c r="AI18" s="5" t="inlineStr"/>
+      <c r="AJ18" s="5" t="inlineStr"/>
+      <c r="AK18" s="5" t="inlineStr"/>
+      <c r="AL18" s="5" t="inlineStr"/>
+      <c r="AM18" s="5" t="inlineStr"/>
+      <c r="AN18" s="5" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AP18" s="4" t="inlineStr"/>
+      <c r="AQ18" s="4" t="inlineStr"/>
+      <c r="AR18" s="4" t="inlineStr"/>
+      <c r="AS18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU18" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV18" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW18" s="5" t="inlineStr"/>
+      <c r="AX18" s="5" t="inlineStr"/>
+      <c r="AY18" s="4" t="inlineStr"/>
+      <c r="AZ18" s="4" t="inlineStr"/>
+      <c r="BA18" s="5" t="inlineStr"/>
+      <c r="BB18" s="5" t="inlineStr"/>
+      <c r="BC18" s="5" t="inlineStr"/>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>MR-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 18</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y19" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE19" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr"/>
+      <c r="AI19" s="5" t="inlineStr"/>
+      <c r="AJ19" s="5" t="inlineStr"/>
+      <c r="AK19" s="5" t="inlineStr"/>
+      <c r="AL19" s="5" t="inlineStr"/>
+      <c r="AM19" s="5" t="inlineStr"/>
+      <c r="AN19" s="5" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AP19" s="4" t="inlineStr"/>
+      <c r="AQ19" s="4" t="inlineStr"/>
+      <c r="AR19" s="4" t="inlineStr"/>
+      <c r="AS19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU19" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV19" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW19" s="5" t="inlineStr"/>
+      <c r="AX19" s="5" t="inlineStr"/>
+      <c r="AY19" s="4" t="inlineStr"/>
+      <c r="AZ19" s="4" t="inlineStr"/>
+      <c r="BA19" s="5" t="inlineStr"/>
+      <c r="BB19" s="5" t="inlineStr"/>
+      <c r="BC19" s="5" t="inlineStr"/>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>MR-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 19</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA20" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB20" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD20" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE20" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr"/>
+      <c r="AI20" s="5" t="inlineStr"/>
+      <c r="AJ20" s="5" t="inlineStr"/>
+      <c r="AK20" s="5" t="inlineStr"/>
+      <c r="AL20" s="5" t="inlineStr"/>
+      <c r="AM20" s="5" t="inlineStr"/>
+      <c r="AN20" s="5" t="inlineStr"/>
+      <c r="AO20" s="4" t="inlineStr"/>
+      <c r="AP20" s="4" t="inlineStr"/>
+      <c r="AQ20" s="4" t="inlineStr"/>
+      <c r="AR20" s="4" t="inlineStr"/>
+      <c r="AS20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU20" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW20" s="5" t="inlineStr"/>
+      <c r="AX20" s="5" t="inlineStr"/>
+      <c r="AY20" s="4" t="inlineStr"/>
+      <c r="AZ20" s="4" t="inlineStr"/>
+      <c r="BA20" s="5" t="inlineStr"/>
+      <c r="BB20" s="5" t="inlineStr"/>
+      <c r="BC20" s="5" t="inlineStr"/>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>MR-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor SEW - CILINDRO SECADORA 20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>SECADO MECANICO</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>SEW-EURODRIVE</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>R97 DRN100L4/BES</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Motorreductor</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>IE3</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>1758</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>IP55</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>CLP 220 mineral</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB21" s="4" t="n">
+        <v>143.379</v>
+      </c>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AD21" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE21" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente inspección</t>
+        </is>
+      </c>
+      <c r="AG21" s="4" t="inlineStr">
+        <is>
+          <t>Datos obtenidos de placa</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr"/>
+      <c r="AI21" s="5" t="inlineStr"/>
+      <c r="AJ21" s="5" t="inlineStr"/>
+      <c r="AK21" s="5" t="inlineStr"/>
+      <c r="AL21" s="5" t="inlineStr"/>
+      <c r="AM21" s="5" t="inlineStr"/>
+      <c r="AN21" s="5" t="inlineStr"/>
+      <c r="AO21" s="4" t="inlineStr"/>
+      <c r="AP21" s="4" t="inlineStr"/>
+      <c r="AQ21" s="4" t="inlineStr"/>
+      <c r="AR21" s="4" t="inlineStr"/>
+      <c r="AS21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU21" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AV21" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW21" s="5" t="inlineStr"/>
+      <c r="AX21" s="5" t="inlineStr"/>
+      <c r="AY21" s="4" t="inlineStr"/>
+      <c r="AZ21" s="4" t="inlineStr"/>
+      <c r="BA21" s="5" t="inlineStr"/>
+      <c r="BB21" s="5" t="inlineStr"/>
+      <c r="BC21" s="5" t="inlineStr"/>
+      <c r="BD21" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BE21" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BF21" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
+        </is>
+      </c>
+      <c r="BG21" s="8" t="inlineStr">
+        <is>
+          <t>SIN MEDICION</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB4"/>
+  <autoFilter ref="A1:BG21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -989,184 +4569,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>INDICADOR</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Total de motores</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
-        <v>3</v>
+      <c r="B2" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Potencia instalada HP</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>230</v>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Motores con medición</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Potencia instalada kW</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>171.58</v>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Motores sin medición</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Motores diagnóstico normal</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>1</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Potencia instalada kW</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Motores con carga alta</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Motores diagnóstico normal</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Motores con carga baja</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Motores con carga alta</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Motores con posible sobrecarga</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Motores con carga baja</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Motores con desbalance de corriente</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Motores con posible sobrecarga</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Motores con desbalance de voltaje</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Motores con desbalance de corriente</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Mayor desbalance de corriente %</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>3.49</v>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Motores con desbalance de voltaje</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Mayor desbalance de voltaje %</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>0.5600000000000001</v>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Mayor desbalance de corriente %</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Carga promedio por corriente %</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>90.16</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Mayor desbalance de voltaje %</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Límite carga baja %</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="11" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Límite carga alta %</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="11" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Límite sobrecarga %</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="11" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Límite desbalance corriente %</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Límite desbalance voltaje %</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="11" t="n">
         <v>1</v>
       </c>
     </row>
